--- a/business_report_forms/024_project_handover_form--business_report_forms.xlsx
+++ b/business_report_forms/024_project_handover_form--business_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>handover_date_time</t>
+          <t>handover_date_time_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Handover Date and Time</t>
+          <t>Handover Date Time 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>handover_notes</t>
+          <t>handover_notes_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>handover_notes</t>
+          <t>Handover Notes 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>project_status_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>Project Status 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>handover_person</t>
+          <t>handover_person_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Handover Person</t>
+          <t>Handover Person 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>project_status_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>Project Status 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>handover_date_time</t>
+          <t>handover_date_time_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Handover Date and Time</t>
+          <t>Handover Date Time 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>handover_person_choices</t>
+          <t>handover_person_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>handover_person_choices</t>
+          <t>handover_person_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>handover_person_choices</t>
+          <t>handover_person_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_3_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_3_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
